--- a/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BW260003</t>
+          <t>1ZRR43520339569305</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BW260004</t>
+          <t>1ZRR43520304831381</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BW260005</t>
+          <t>1ZRR43520318249315</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BW260006</t>
+          <t>1ZRR43520317439326</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BW260007</t>
+          <t>1ZRR43520304641336</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BW260008</t>
+          <t>1ZRR43520314255342</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BW260009</t>
+          <t>1ZRR43520300681354</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BW260010</t>
+          <t>1ZRR43520318319365</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BW260011</t>
+          <t>1ZRR43520301569377</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">

--- a/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:AE55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,31 @@
           <t>__SYSTEM_META__</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>해외수하인주소</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>해외수하인전화번호</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>실중량(kg)</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>매출실중량(kg)</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>매입실중량(kg)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -665,6 +690,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -783,6 +813,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -901,6 +936,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1019,6 +1059,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1137,6 +1182,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1255,6 +1305,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1373,6 +1428,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1491,6 +1551,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1609,6 +1674,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1727,6 +1797,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1845,6 +1920,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1963,6 +2043,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2081,6 +2166,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2199,6 +2289,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2317,6 +2412,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2435,6 +2535,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2553,6 +2658,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2671,6 +2781,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2789,6 +2904,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2907,6 +3027,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3029,6 +3154,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3147,6 +3277,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3265,6 +3400,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3383,6 +3523,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3501,6 +3646,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3619,6 +3769,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3737,6 +3892,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3855,6 +4015,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3973,6 +4138,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4091,6 +4261,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4213,6 +4388,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4331,6 +4511,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4449,6 +4634,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4567,6 +4757,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4685,6 +4880,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4803,6 +5003,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4921,6 +5126,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5039,6 +5249,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5157,6 +5372,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5275,6 +5495,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5393,6 +5618,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5511,6 +5741,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5629,6 +5864,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5747,6 +5987,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5766,7 +6011,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BW260013</t>
+          <t>1ZRR43520302505399</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5857,13 +6102,24 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -5884,7 +6140,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BW260014</t>
+          <t>1ZRR43520308991406</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5975,13 +6231,24 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -6002,7 +6269,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BW260015</t>
+          <t>1ZRR43520302716938</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6100,6 +6367,17 @@
         <is>
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -6120,7 +6398,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BW260016</t>
+          <t>1ZRR43520318689411</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6211,13 +6489,24 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -6337,6 +6626,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6455,6 +6749,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6573,6 +6872,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6691,6 +6995,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6809,6 +7118,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6927,6 +7241,11 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr"/>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr"/>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr"/>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr"/>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr"/>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr"/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr"/>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr"/>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr"/>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-19.xlsx
@@ -7,7 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bumwoon_Integrated_Backup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="B_L데이터" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="일계표_입출금장부" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="경비_지출내역" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="거래처미팅노트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="업무용일지" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="시스템설정" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7250,4 +7255,583 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>적요</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>수입 (+)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>통장잔액 법인통장</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>남양김태호 저녁식대</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>주유비(차량유지비)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5710</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>아코 박수진 저녁식대</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>176000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>맥 이지훈 저녁식대</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>리턴의원 인천 용달비</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>넥서스 파마 고촌 용달입고비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>필러 20박스 윤세형 입고비용</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>적요</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>남양김태호 저녁식대</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>주유비 (차량유지비)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>주유비 5710</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>아코 박수진 저녁식대</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>176000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>맥 이지훈팀장 저녁식대</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>리턴의원 용달비(회사-인천)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>정해균</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>넥세스파마 용달비(회사-K-GLOBAL)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>정해균</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>신규업체 20박스 용달비(회사 - 인천)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>정해균</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>수입 (+)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>기타 영업수입</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1365000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>통장 잔액</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>__SYSTEM_META__</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": 1365000, "금액(원)": 1365000, "적요": "통장잔액 법인통장"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>